--- a/customers.xlsx
+++ b/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3413000</v>
+        <v>3183000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/06/21 - 19:57</t>
+          <t>1405/06/22 - 09:58</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6522000</v>
+        <v>6618000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/06/18 - 19:14</t>
+          <t>1405/06/22 - 09:58</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3190000</v>
+        <v>2960000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/06/21 - 19:56</t>
+          <t>1405/06/22 - 09:57</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -523,11 +523,11 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>589000</v>
+        <v>551000</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1405/06/21 - 19:59</t>
+          <t>1405/06/22 - 09:59</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -546,11 +546,11 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>580000</v>
+        <v>150000</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1405/06/21 - 19:58</t>
+          <t>1405/06/22 - 09:58</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4490000</v>
+        <v>4790000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/06/20 - 16:36</t>
+          <t>1405/06/23 - 17:31</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3190600</v>
+        <v>3452600</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1405/06/18 - 19:12</t>
+          <t>1405/06/25 - 17:17</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3452600</v>
+        <v>2952600</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1405/06/25 - 17:17</t>
+          <t>1405/06/27 - 16:53</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2952600</v>
+        <v>3102600</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1405/06/27 - 16:53</t>
+          <t>1405/06/27 - 16:55</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3475000</v>
+        <v>3715000</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1405/06/08 - 16:29</t>
+          <t>1405/06/27 - 18:07</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4790000</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/06/23 - 17:31</t>
+          <t>1405/07/02 - 15:44</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -753,11 +753,11 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1405/06/02 - 11:28</t>
+          <t>1405/07/02 - 15:45</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2960000</v>
+        <v>3010000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/06/22 - 09:57</t>
+          <t>1405/07/02 - 20:47</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3102600</v>
+        <v>3282600</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1405/06/27 - 16:55</t>
+          <t>1405/07/03 - 15:20</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3183000</v>
+        <v>3408000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/06/22 - 09:58</t>
+          <t>1405/07/04 - 19:00</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6618000</v>
+        <v>6843000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/06/22 - 09:58</t>
+          <t>1405/07/04 - 19:01</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3010000</v>
+        <v>3235000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/02 - 20:47</t>
+          <t>1405/07/04 - 18:59</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3235000</v>
+        <v>3285000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/04 - 18:59</t>
+          <t>1405/07/04 - 19:05</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6843000</v>
+        <v>6893000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/04 - 19:01</t>
+          <t>1405/07/06 - 18:55</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -592,11 +592,11 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1468500</v>
+        <v>1538500</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1405/06/12 - 19:10</t>
+          <t>1405/07/06 - 18:55</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -592,11 +592,11 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1538500</v>
+        <v>1583500</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1405/07/06 - 18:55</t>
+          <t>1405/07/06 - 19:32</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3285000</v>
+        <v>3205000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/04 - 19:05</t>
+          <t>1405/07/06 - 19:45</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3205000</v>
+        <v>3221000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/06 - 19:45</t>
+          <t>1405/07/07 - 19:08</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/07/02 - 15:44</t>
+          <t>1405/07/09 - 17:44</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6893000</v>
+        <v>6655000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/06 - 18:55</t>
+          <t>1405/07/09 - 21:08</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>230000</v>
+        <v>580000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/07/09 - 17:44</t>
+          <t>1405/07/10 - 15:52</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6655000</v>
+        <v>6671000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/09 - 21:08</t>
+          <t>1405/07/10 - 16:41</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3221000</v>
+        <v>3285000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/07 - 19:08</t>
+          <t>1405/07/10 - 16:40</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -767,11 +767,27 @@
       </c>
     </row>
     <row r="16" ht="27.75" customHeight="1">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
+      <c r="A16" s="3" t="n">
+        <v>3011</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>علی رحمتی</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>1405/07/10 - 18:03</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>ali.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="27.75" customHeight="1">
       <c r="A17" s="3" t="n"/>

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -776,11 +776,11 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1405/07/10 - 18:03</t>
+          <t>1405/07/10 - 18:05</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3715000</v>
+        <v>3965000</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1405/06/27 - 18:07</t>
+          <t>1405/07/10 - 19:20</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3408000</v>
+        <v>3608000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/07/04 - 19:00</t>
+          <t>1405/07/10 - 19:23</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6671000</v>
+        <v>6871000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/10 - 16:41</t>
+          <t>1405/07/10 - 19:24</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3285000</v>
+        <v>3485000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/10 - 16:40</t>
+          <t>1405/07/10 - 19:23</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -523,11 +523,11 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>551000</v>
+        <v>301000</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1405/06/22 - 09:59</t>
+          <t>1405/07/10 - 20:05</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3608000</v>
+        <v>2608000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/07/10 - 19:23</t>
+          <t>1405/07/12 - 19:17</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -730,11 +730,11 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4981000</v>
+        <v>-2219000</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>1405/06/08 - 16:23</t>
+          <t>1405/07/12 - 19:28</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -753,11 +753,11 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1405/07/02 - 15:45</t>
+          <t>1405/07/12 - 20:42</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -523,11 +523,11 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>301000</v>
+        <v>-99000</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1405/07/10 - 20:05</t>
+          <t>1405/07/13 - 17:51</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -776,11 +776,11 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>700000</v>
+        <v>1100000</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1405/07/10 - 18:05</t>
+          <t>1405/07/13 - 18:04</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>580000</v>
+        <v>952000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/07/10 - 15:52</t>
+          <t>1405/07/13 - 18:43</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3485000</v>
+        <v>1985000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/10 - 19:23</t>
+          <t>1405/07/14 - 17:47</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2608000</v>
+        <v>2648000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/07/12 - 19:17</t>
+          <t>1405/07/14 - 19:30</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -523,11 +523,11 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-99000</v>
+        <v>-59000</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1405/07/13 - 17:51</t>
+          <t>1405/07/14 - 19:31</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>952000</v>
+        <v>1342000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/07/13 - 18:43</t>
+          <t>1405/07/15 - 16:34</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1342000</v>
+        <v>1532000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/07/15 - 16:34</t>
+          <t>1405/07/16 - 16:27</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1405/07/13 - 18:04</t>
+          <t>1405/07/16 - 16:30</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -776,11 +776,11 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1100000</v>
+        <v>1200000</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1405/07/16 - 16:30</t>
+          <t>1405/07/16 - 18:17</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2648000</v>
+        <v>2608000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/07/14 - 19:30</t>
+          <t>1405/07/16 - 19:37</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1985000</v>
+        <v>2025000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/14 - 17:47</t>
+          <t>1405/07/16 - 19:37</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -730,11 +730,11 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-2219000</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>1405/07/12 - 19:28</t>
+          <t>1405/07/17 - 15:46</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -523,11 +523,11 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-59000</v>
+        <v>-9000</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1405/07/14 - 19:31</t>
+          <t>1405/07/17 - 17:44</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2608000</v>
+        <v>2833000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/07/16 - 19:37</t>
+          <t>1405/07/17 - 17:48</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6871000</v>
+        <v>7166000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/10 - 19:24</t>
+          <t>1405/07/17 - 17:47</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2025000</v>
+        <v>2250000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/16 - 19:37</t>
+          <t>1405/07/17 - 17:48</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -753,11 +753,11 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1405/07/12 - 20:42</t>
+          <t>1405/07/19 - 16:22</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1532000</v>
+        <v>1722000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/07/16 - 16:27</t>
+          <t>1405/07/19 - 16:25</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2250000</v>
+        <v>2430000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/17 - 17:48</t>
+          <t>1405/07/19 - 17:40</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7166000</v>
+        <v>7216000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/17 - 17:47</t>
+          <t>1405/07/19 - 18:09</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -776,11 +776,11 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1200000</v>
+        <v>1887000</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1405/07/16 - 18:17</t>
+          <t>1405/07/19 - 19:05</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2430000</v>
+        <v>2730000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/19 - 17:40</t>
+          <t>1405/07/21 - 16:43</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -592,11 +592,11 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1583500</v>
+        <v>2363500</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1405/07/06 - 19:32</t>
+          <t>1405/07/21 - 16:45</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1722000</v>
+        <v>2115000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/07/19 - 16:25</t>
+          <t>1405/07/21 - 16:45</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -638,11 +638,11 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>6450000</v>
+        <v>1450000</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1405/04/19 - 19:43</t>
+          <t>1405/07/22 - 16:29</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7216000</v>
+        <v>7266000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/19 - 18:09</t>
+          <t>1405/07/22 - 17:13</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1405/07/19 - 19:05</t>
+          <t>1405/07/22 - 18:14</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2115000</v>
+        <v>2515000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/07/21 - 16:45</t>
+          <t>1405/07/22 - 18:18</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -776,11 +776,11 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1887000</v>
+        <v>87000</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1405/07/22 - 18:14</t>
+          <t>1405/07/22 - 18:53</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7266000</v>
+        <v>7366000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/22 - 17:13</t>
+          <t>1405/07/23 - 16:18</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7366000</v>
+        <v>7466000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/23 - 16:18</t>
+          <t>1405/07/23 - 17:02</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2833000</v>
+        <v>3022000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/07/17 - 17:48</t>
+          <t>1405/07/24 - 16:55</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7466000</v>
+        <v>7680000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/23 - 17:02</t>
+          <t>1405/07/24 - 16:59</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2730000</v>
+        <v>2974000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/21 - 16:43</t>
+          <t>1405/07/24 - 16:53</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -546,11 +546,11 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>150000</v>
+        <v>339000</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1405/06/22 - 09:58</t>
+          <t>1405/07/24 - 16:54</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -592,11 +592,11 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2363500</v>
+        <v>2552500</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1405/07/21 - 16:45</t>
+          <t>1405/07/24 - 16:57</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3282600</v>
+        <v>3471600</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1405/07/03 - 15:20</t>
+          <t>1405/07/24 - 16:55</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3471600</v>
+        <v>3282600</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1405/07/24 - 16:55</t>
+          <t>1405/07/24 - 18:28</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -776,11 +776,11 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>87000</v>
+        <v>447000</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1405/07/22 - 18:53</t>
+          <t>1405/07/24 - 18:42</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -546,11 +546,11 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>339000</v>
+        <v>519000</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1405/07/24 - 16:54</t>
+          <t>1405/07/24 - 19:00</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -753,11 +753,11 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1405/07/19 - 16:22</t>
+          <t>1405/07/24 - 21:11</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3282600</v>
+        <v>3342600</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1405/07/24 - 18:28</t>
+          <t>1405/07/24 - 21:12</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2974000</v>
+        <v>2810000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/24 - 16:53</t>
+          <t>1405/07/25 - 18:42</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2515000</v>
+        <v>2705000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/07/22 - 18:18</t>
+          <t>1405/07/25 - 18:44</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7680000</v>
+        <v>7710000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/24 - 16:59</t>
+          <t>1405/07/25 - 19:44</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3022000</v>
+        <v>2833000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/07/24 - 16:55</t>
+          <t>1405/07/25 - 20:06</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -753,11 +753,11 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>800000</v>
+        <v>927000</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1405/07/24 - 21:11</t>
+          <t>1405/07/26 - 18:51</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/07/25 - 18:44</t>
+          <t>1405/07/27 - 17:22</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -776,11 +776,11 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>447000</v>
+        <v>1043000</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1405/07/24 - 18:42</t>
+          <t>1405/07/27 - 18:18</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2810000</v>
+        <v>2845000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/25 - 18:42</t>
+          <t>1405/07/27 - 19:54</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/07/27 - 17:22</t>
+          <t>1405/07/28 - 17:26</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3342600</v>
+        <v>3492600</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1405/07/24 - 21:12</t>
+          <t>1405/07/28 - 20:23</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2833000</v>
+        <v>3103000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/07/25 - 20:06</t>
+          <t>1405/07/29 - 18:19</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7710000</v>
+        <v>8030000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/25 - 19:44</t>
+          <t>1405/07/29 - 18:19</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2845000</v>
+        <v>3115000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/27 - 19:54</t>
+          <t>1405/07/29 - 18:18</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -546,11 +546,11 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>519000</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1405/07/24 - 19:00</t>
+          <t>1405/07/29 - 19:17</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -523,11 +523,11 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-9000</v>
+        <v>-549000</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1405/07/17 - 17:44</t>
+          <t>1405/07/29 - 19:37</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8030000</v>
+        <v>5030000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/29 - 18:19</t>
+          <t>1405/07/30 - 14:57</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -753,11 +753,11 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>927000</v>
+        <v>-3000</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1405/07/26 - 18:51</t>
+          <t>1405/07/30 - 14:57</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -592,11 +592,11 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2552500</v>
+        <v>2702500</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1405/07/24 - 16:57</t>
+          <t>1405/07/30 - 20:43</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3103000</v>
+        <v>2103000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/07/29 - 18:19</t>
+          <t>1405/07/30 - 21:05</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -776,11 +776,11 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1043000</v>
+        <v>1673000</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1405/07/27 - 18:18</t>
+          <t>1405/08/01 - 16:22</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3115000</v>
+        <v>3205000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/07/29 - 18:18</t>
+          <t>1405/08/01 - 17:49</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/07/28 - 17:26</t>
+          <t>1405/08/01 - 18:33</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/08/01 - 18:33</t>
+          <t>1405/08/02 - 19:00</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3056000</v>
+        <v>3151000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/08/02 - 19:00</t>
+          <t>1405/08/03 - 18:37</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -776,11 +776,11 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1673000</v>
+        <v>2427000</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1405/08/01 - 16:22</t>
+          <t>1405/08/04 - 18:03</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/08/03 - 18:37</t>
+          <t>1405/08/04 - 18:44</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -592,11 +592,11 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2702500</v>
+        <v>1202500</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1405/07/30 - 20:43</t>
+          <t>1405/08/05 - 18:43</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5030000</v>
+        <v>5100000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/07/30 - 14:57</t>
+          <t>1405/08/05 - 19:08</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -523,11 +523,11 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-549000</v>
+        <v>-184000</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1405/07/29 - 19:37</t>
+          <t>1405/08/05 - 19:08</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2103000</v>
+        <v>2238000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/07/30 - 21:05</t>
+          <t>1405/08/05 - 19:12</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5100000</v>
+        <v>5235000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/08/05 - 19:08</t>
+          <t>1405/08/05 - 19:12</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3205000</v>
+        <v>3250000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/08/01 - 17:49</t>
+          <t>1405/08/05 - 19:11</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5235000</v>
+        <v>5165000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/08/05 - 19:12</t>
+          <t>1405/08/05 - 19:22</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/08/04 - 18:44</t>
+          <t>1405/08/06 - 19:58</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3492600</v>
+        <v>1492600</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1405/07/28 - 20:23</t>
+          <t>1405/08/07 - 20:53</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2238000</v>
+        <v>2363000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/08/05 - 19:12</t>
+          <t>1405/08/07 - 21:27</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5165000</v>
+        <v>5290000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/08/05 - 19:22</t>
+          <t>1405/08/07 - 21:28</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3250000</v>
+        <v>3510000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/08/05 - 19:11</t>
+          <t>1405/08/07 - 21:25</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -546,11 +546,11 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1405/07/29 - 19:17</t>
+          <t>1405/08/07 - 21:26</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3965000</v>
+        <v>4465000</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1405/07/10 - 19:20</t>
+          <t>1405/08/08 - 13:35</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1492600</v>
+        <v>1672600</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1405/08/07 - 20:53</t>
+          <t>1405/08/08 - 13:35</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -776,11 +776,11 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>2427000</v>
+        <v>2922000</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1405/08/04 - 18:03</t>
+          <t>1405/08/08 - 18:00</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1672600</v>
+        <v>1872600</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1405/08/08 - 13:35</t>
+          <t>1405/08/08 - 19:27</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">

--- a/customers.xlsx
+++ b/customers.xlsx
@@ -592,11 +592,11 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1202500</v>
+        <v>762500</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1405/08/05 - 18:43</t>
+          <t>1405/08/09 - 19:39</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
